--- a/cet4/result/53_校园青春_学霸女神的成长路/53_校园青春_学霸女神的成长路_学习版.xlsx
+++ b/cet4/result/53_校园青春_学霸女神的成长路/53_校园青春_学霸女神的成长路_学习版.xlsx
@@ -397,787 +397,633 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D44"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>dawn</v>
       </c>
       <c r="B2" t="str">
-        <v>dawn</v>
+        <v>/dɔːn/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>黎明</v>
       </c>
-      <c r="D2" t="str">
-        <v>dawn(黎明)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>inside</v>
       </c>
       <c r="B3" t="str">
-        <v>inside</v>
+        <v>/ˌɪnˈsaɪd/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv./prep.</v>
+      </c>
+      <c r="D3" t="str">
         <v>里面</v>
       </c>
-      <c r="D3" t="str">
-        <v>inside(里面)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>kitchen</v>
       </c>
       <c r="B4" t="str">
-        <v>kitchen</v>
+        <v>/ˈkɪtʃɪn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>厨房</v>
       </c>
-      <c r="D4" t="str">
-        <v>kitchen(厨房)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>breakfast</v>
       </c>
       <c r="B5" t="str">
-        <v>breakfast</v>
+        <v>/ˈbrekfəst/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>早餐</v>
       </c>
-      <c r="D5" t="str">
-        <v>breakfast(早餐)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>intimate</v>
       </c>
       <c r="B6" t="str">
-        <v>intimate</v>
+        <v>/ˈɪntɪmət/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>亲密的</v>
       </c>
-      <c r="D6" t="str">
-        <v>intimate(亲密的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>time</v>
       </c>
       <c r="B7" t="str">
-        <v>time</v>
+        <v>/taɪm/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>时间</v>
       </c>
-      <c r="D7" t="str">
-        <v>time(时间)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>have</v>
       </c>
       <c r="B8" t="str">
-        <v>have</v>
+        <v>/həv,əv,hæv/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./aux.</v>
+      </c>
+      <c r="D8" t="str">
         <v>有</v>
       </c>
-      <c r="D8" t="str">
-        <v>have(有)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>meat</v>
       </c>
       <c r="B9" t="str">
-        <v>meat</v>
+        <v>/miːt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>肉</v>
       </c>
-      <c r="D9" t="str">
-        <v>meat(肉)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>dear</v>
       </c>
       <c r="B10" t="str">
-        <v>dear</v>
+        <v>/dɪr/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj./int.</v>
+      </c>
+      <c r="D10" t="str">
         <v>亲爱的</v>
       </c>
-      <c r="D10" t="str">
-        <v>dear(亲爱的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>hasty</v>
       </c>
       <c r="B11" t="str">
-        <v>hasty</v>
+        <v>/ˈheɪsti/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>轻率的</v>
       </c>
-      <c r="D11" t="str">
-        <v>hasty(轻率的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>corner</v>
       </c>
       <c r="B12" t="str">
-        <v>corner</v>
+        <v>/ˈkɔːrnər/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>角落</v>
       </c>
-      <c r="D12" t="str">
-        <v>corner(角落)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>exam</v>
       </c>
       <c r="B13" t="str">
-        <v>exam</v>
+        <v>/ɪɡˈzæm/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>考试</v>
       </c>
-      <c r="D13" t="str">
-        <v>exam(考试)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>atmosphere</v>
       </c>
       <c r="B14" t="str">
-        <v>atmosphere</v>
+        <v>/ˈætməsfɪr/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>气氛</v>
       </c>
-      <c r="D14" t="str">
-        <v>atmosphere(气氛)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>talk</v>
       </c>
       <c r="B15" t="str">
-        <v>talk</v>
+        <v>/tɔːk/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D15" t="str">
         <v>谈话</v>
       </c>
-      <c r="D15" t="str">
-        <v>talk(谈话)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>sit</v>
       </c>
       <c r="B16" t="str">
-        <v>sit</v>
+        <v>/sɪt/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>坐</v>
       </c>
-      <c r="D16" t="str">
-        <v>sit(坐)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>theoretical</v>
       </c>
       <c r="B17" t="str">
-        <v>theoretical</v>
+        <v>/ˌθiːəˈretɪkl/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>理论的</v>
       </c>
-      <c r="D17" t="str">
-        <v>theoretical(理论的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>while</v>
       </c>
       <c r="B18" t="str">
-        <v>time</v>
+        <v>/waɪl/</v>
       </c>
       <c r="C18" t="str">
-        <v>时间</v>
+        <v>n./vt./prep./conj.</v>
       </c>
       <c r="D18" t="str">
-        <v>time(时间)📢</v>
+        <v>当...的时候</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>phone</v>
       </c>
       <c r="B19" t="str">
-        <v>while</v>
+        <v>/foʊn/</v>
       </c>
       <c r="C19" t="str">
-        <v>当...的时候</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D19" t="str">
-        <v>while(当...的时候)📢</v>
+        <v>电话</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>midday</v>
       </c>
       <c r="B20" t="str">
-        <v>phone</v>
+        <v>/ˌmɪdˈdeɪ/</v>
       </c>
       <c r="C20" t="str">
-        <v>电话</v>
+        <v>n./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>phone(电话)📢</v>
+        <v>中午</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>commonly</v>
       </c>
       <c r="B21" t="str">
-        <v>meat</v>
+        <v>/ˈkɑːmənli/</v>
       </c>
       <c r="C21" t="str">
-        <v>肉</v>
+        <v>v./adv.</v>
       </c>
       <c r="D21" t="str">
-        <v>meat(肉)📢</v>
+        <v>通常</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>immense</v>
       </c>
       <c r="B22" t="str">
-        <v>midday</v>
+        <v>/ɪˈmens/</v>
       </c>
       <c r="C22" t="str">
-        <v>中午</v>
+        <v>adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>midday(中午)📢</v>
+        <v>巨大的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>honest</v>
       </c>
       <c r="B23" t="str">
-        <v>commonly</v>
+        <v>/ˈɑːnɪst/</v>
       </c>
       <c r="C23" t="str">
-        <v>通常</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>commonly(通常)📢</v>
+        <v>诚实的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>experimental</v>
       </c>
       <c r="B24" t="str">
-        <v>immense</v>
+        <v>/ɪkˌsperɪˈmentl/</v>
       </c>
       <c r="C24" t="str">
-        <v>巨大的</v>
+        <v>adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>immense(巨大的)📢</v>
+        <v>实验的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>funeral</v>
       </c>
       <c r="B25" t="str">
-        <v>honest</v>
+        <v>/ˈfjuːnərəl/</v>
       </c>
       <c r="C25" t="str">
-        <v>诚实的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>honest(诚实的)📢</v>
+        <v>葬礼</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>hateful</v>
       </c>
       <c r="B26" t="str">
-        <v>experimental</v>
+        <v>/ˈheɪtfl/</v>
       </c>
       <c r="C26" t="str">
-        <v>实验的</v>
+        <v>adj.</v>
       </c>
       <c r="D26" t="str">
-        <v>experimental(实验的)📢</v>
+        <v>可憎的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>tolerance</v>
       </c>
       <c r="B27" t="str">
-        <v>funeral</v>
+        <v>/ˈtɑːlərəns/</v>
       </c>
       <c r="C27" t="str">
-        <v>葬礼</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>funeral(葬礼)📢</v>
+        <v>宽容</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>game</v>
       </c>
       <c r="B28" t="str">
-        <v>hateful</v>
+        <v>/ɡeɪm/</v>
       </c>
       <c r="C28" t="str">
-        <v>可憎的</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>hateful(可憎的)📢</v>
+        <v>游戏</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>realm</v>
       </c>
       <c r="B29" t="str">
-        <v>tolerance</v>
+        <v>/relm/</v>
       </c>
       <c r="C29" t="str">
-        <v>宽容</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>tolerance(宽容)📢</v>
+        <v>领域</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>interpreter</v>
       </c>
       <c r="B30" t="str">
-        <v>game</v>
+        <v>/ɪnˈtɜːrprətər/</v>
       </c>
       <c r="C30" t="str">
-        <v>游戏</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>game(游戏)📢</v>
+        <v>解释者</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>man</v>
       </c>
       <c r="B31" t="str">
-        <v>realm</v>
+        <v>/mæn/</v>
       </c>
       <c r="C31" t="str">
-        <v>领域</v>
+        <v>n./vt.</v>
       </c>
       <c r="D31" t="str">
-        <v>realm(领域)📢</v>
+        <v>人</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>conversion</v>
       </c>
       <c r="B32" t="str">
-        <v>interpreter</v>
+        <v>/kənˈvɜːrʒn/</v>
       </c>
       <c r="C32" t="str">
-        <v>解释者</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>interpreter(解释者)📢</v>
+        <v>转换</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>again</v>
       </c>
       <c r="B33" t="str">
-        <v>man</v>
+        <v>/əˈɡen,əˈɡeɪn/</v>
       </c>
       <c r="C33" t="str">
-        <v>人</v>
+        <v>n./v./adv.</v>
       </c>
       <c r="D33" t="str">
-        <v>man(人)📢</v>
+        <v>再次</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>assess</v>
       </c>
       <c r="B34" t="str">
-        <v>dear</v>
+        <v>/əˈses/</v>
       </c>
       <c r="C34" t="str">
-        <v>亲爱的</v>
+        <v>vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>dear(亲爱的)📢</v>
+        <v>评定</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>kill</v>
       </c>
       <c r="B35" t="str">
-        <v>while</v>
+        <v>/kɪl/</v>
       </c>
       <c r="C35" t="str">
-        <v>当...的时候</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>while(当...的时候)📢</v>
+        <v>杀死</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>screen</v>
       </c>
       <c r="B36" t="str">
-        <v>conversion</v>
+        <v>/skriːn/</v>
       </c>
       <c r="C36" t="str">
-        <v>转换</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>conversion(转换)📢</v>
+        <v>屏幕</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>fresh</v>
       </c>
       <c r="B37" t="str">
-        <v>again</v>
+        <v>/freʃ/</v>
       </c>
       <c r="C37" t="str">
-        <v>再次</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D37" t="str">
-        <v>again(再次)📢</v>
+        <v>新鲜的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>retire</v>
       </c>
       <c r="B38" t="str">
-        <v>talk</v>
+        <v>/rɪˈtaɪər/</v>
       </c>
       <c r="C38" t="str">
-        <v>谈话</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>talk(谈话)📢</v>
+        <v>退休</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>severely</v>
       </c>
       <c r="B39" t="str">
-        <v>assess</v>
+        <v>/sɪˈvɪrli/</v>
       </c>
       <c r="C39" t="str">
-        <v>评定</v>
+        <v>v./adv.</v>
       </c>
       <c r="D39" t="str">
-        <v>assess(评定)📢</v>
+        <v>严重地</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>mutter</v>
       </c>
       <c r="B40" t="str">
-        <v>kill</v>
+        <v>/ˈmʌtər/</v>
       </c>
       <c r="C40" t="str">
-        <v>杀死</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>kill(杀死)📢</v>
+        <v>咕哝</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>certain</v>
       </c>
       <c r="B41" t="str">
-        <v>screen</v>
+        <v>/ˈsɜːrtn/</v>
       </c>
       <c r="C41" t="str">
-        <v>屏幕</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D41" t="str">
-        <v>screen(屏幕)📢</v>
+        <v>某一</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>ice</v>
       </c>
       <c r="B42" t="str">
-        <v>fresh</v>
+        <v>/aɪs/</v>
       </c>
       <c r="C42" t="str">
-        <v>新鲜的</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>fresh(新鲜的)📢</v>
+        <v>冰</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>treaty</v>
       </c>
       <c r="B43" t="str">
-        <v>experimental</v>
+        <v>/ˈtriːti/</v>
       </c>
       <c r="C43" t="str">
-        <v>实验的</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>experimental(实验的)📢</v>
+        <v>条约</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>twinkle</v>
       </c>
       <c r="B44" t="str">
-        <v>retire</v>
+        <v>/ˈtwɪŋkl/</v>
       </c>
       <c r="C44" t="str">
-        <v>退休</v>
+        <v>n./v.</v>
       </c>
       <c r="D44" t="str">
-        <v>retire(退休)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>atmosphere</v>
-      </c>
-      <c r="C45" t="str">
-        <v>气氛</v>
-      </c>
-      <c r="D45" t="str">
-        <v>atmosphere(气氛)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>severely</v>
-      </c>
-      <c r="C46" t="str">
-        <v>严重地</v>
-      </c>
-      <c r="D46" t="str">
-        <v>severely(严重地)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>mutter</v>
-      </c>
-      <c r="C47" t="str">
-        <v>咕哝</v>
-      </c>
-      <c r="D47" t="str">
-        <v>mutter(咕哝)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>certain</v>
-      </c>
-      <c r="C48" t="str">
-        <v>某一</v>
-      </c>
-      <c r="D48" t="str">
-        <v>certain(某一)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>immense</v>
-      </c>
-      <c r="C49" t="str">
-        <v>巨大的</v>
-      </c>
-      <c r="D49" t="str">
-        <v>immense(巨大的)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>sit</v>
-      </c>
-      <c r="C50" t="str">
-        <v>坐</v>
-      </c>
-      <c r="D50" t="str">
-        <v>sit(坐)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>kitchen</v>
-      </c>
-      <c r="C51" t="str">
-        <v>厨房</v>
-      </c>
-      <c r="D51" t="str">
-        <v>kitchen(厨房)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>mutter</v>
-      </c>
-      <c r="C52" t="str">
-        <v>咕哝</v>
-      </c>
-      <c r="D52" t="str">
-        <v>mutter(咕哝)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>ice</v>
-      </c>
-      <c r="C53" t="str">
-        <v>冰</v>
-      </c>
-      <c r="D53" t="str">
-        <v>ice(冰)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>treaty</v>
-      </c>
-      <c r="C54" t="str">
-        <v>条约</v>
-      </c>
-      <c r="D54" t="str">
-        <v>treaty(条约)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>twinkle</v>
-      </c>
-      <c r="C55" t="str">
         <v>闪烁</v>
-      </c>
-      <c r="D55" t="str">
-        <v>twinkle(闪烁)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>